--- a/docs/eu/StructureDefinition-ImComposition.xlsx
+++ b/docs/eu/StructureDefinition-ImComposition.xlsx
@@ -506,7 +506,7 @@
     <t>informationRecipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/information-recipient|0.1.1}
+    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/information-recipient|1.2.0}
 </t>
   </si>
   <si>

--- a/docs/eu/StructureDefinition-ImComposition.xlsx
+++ b/docs/eu/StructureDefinition-ImComposition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>0.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -1497,7 +1497,7 @@
     <t>Composition.event:procedure.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableReference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImProcedure|0.0.1)
+    <t xml:space="preserve">CodeableReference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImProcedure|0.0.2)
 </t>
   </si>
   <si>
@@ -1980,7 +1980,7 @@
     <t>Composition.section:procedure.entry:procedure</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImProcedure|0.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImProcedure|0.0.2)
 </t>
   </si>
   <si>
@@ -2111,7 +2111,7 @@
     <t>finding</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImFinding|0.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImFinding|0.0.2)
 </t>
   </si>
   <si>
@@ -2121,7 +2121,7 @@
     <t>keyimage</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImKeyImageDocumentReference|0.0.1|http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImKeyImageImagingSelection|0.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImKeyImageDocumentReference|0.0.2|http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImKeyImageImagingSelection|0.0.2)
 </t>
   </si>
   <si>
